--- a/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
+++ b/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25900" windowHeight="13900" tabRatio="740" activeTab="1"/>
+    <workbookView windowHeight="14460" tabRatio="740"/>
   </bookViews>
   <sheets>
     <sheet name="Module" sheetId="19" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="217">
   <si>
     <t>moduleCode</t>
   </si>
@@ -218,6 +218,27 @@
   </si>
   <si>
     <t>icon-graduation</t>
+  </si>
+  <si>
+    <t>__id__cms_ai</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>AI助手</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>https://vue.jeesite.com/cms/chat/index</t>
+  </si>
+  <si>
+    <t>_blank</t>
+  </si>
+  <si>
+    <t>icon-bubble</t>
   </si>
   <si>
     <t>dictType</t>
@@ -316,9 +337,6 @@
     </r>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>基础主题</t>
   </si>
   <si>
@@ -505,10 +523,10 @@
     <t>JeeSite 快速开发平台</t>
   </si>
   <si>
-    <t>JeeSite 快速开发平台，不仅仅是一个后台开发框架，它是一个企业级快速开发解决方案，后端基于经典组合 Spring Boot、Shiro、MyBatis，前端采用 Beetl、Bootstrap、AdminLTE 经典开发模式，或者分离版 Vue3、Vite、Ant Design Vue、TypeScript、Vben Admin 最先进技术栈。提供在线代码生成功能，支持 Spring Cloud 架构，分布式，微服务，微内核，信息化领域的专家。</t>
-  </si>
-  <si>
-    <t>&lt;!--HTML--&gt;&lt;p&gt;Copyright © 2024 演示站 - Powered By JeeSite V5&lt;/p&gt;</t>
+    <t>JeeSite 快速开发平台，低代码，轻量级，不仅仅是一个后台开发框架，它是一个企业级快速开发解决方案，后端基于经典组合 Spring Boot、Shiro、MyBatis，前端采用分离版 Vue3、Vite、Ant Design Vue、TypeScript、Vben Admin 最先进技术栈，或者 Beetl、Bootstrap、AdminLTE 经典开发模式。提供在线代码生成功能，支持 Spring Cloud 架构，分布式，微服务，微内核，信息化领域的专家。</t>
+  </si>
+  <si>
+    <t>&lt;!--HTML--&gt;&lt;p&gt;Copyright © 2026 演示站 - Powered By JeeSite V5&lt;/p&gt;</t>
   </si>
   <si>
     <t>index</t>
@@ -1350,7 +1368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1390,6 +1408,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1791,8 +1812,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9.10714285714286" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.2232142857143" style="4" customWidth="1"/>
@@ -2057,7 +2078,49 @@
         <v>29</v>
       </c>
     </row>
+    <row r="7" ht="17" spans="1:16">
+      <c r="A7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="N7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I7" r:id="rId3" display="https://vue.jeesite.com/cms/chat/index"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2079,21 +2142,21 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>29</v>
@@ -2101,10 +2164,10 @@
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>29</v>
@@ -2112,10 +2175,10 @@
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>29</v>
@@ -2123,10 +2186,10 @@
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>29</v>
@@ -2134,10 +2197,10 @@
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>29</v>
@@ -2145,10 +2208,10 @@
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>29</v>
@@ -2156,10 +2219,10 @@
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>29</v>
@@ -2167,10 +2230,10 @@
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>29</v>
@@ -2204,37 +2267,37 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="17" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:11">
@@ -2242,13 +2305,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>25</v>
@@ -2260,7 +2323,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:11">
@@ -2268,16 +2331,16 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>34</v>
@@ -2286,7 +2349,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:11">
@@ -2294,16 +2357,16 @@
         <v>32</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>40</v>
@@ -2312,7 +2375,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:11">
@@ -2320,16 +2383,16 @@
         <v>32</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>45</v>
@@ -2338,7 +2401,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:11">
@@ -2346,16 +2409,16 @@
         <v>32</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>50</v>
@@ -2364,7 +2427,7 @@
         <v>29</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:11">
@@ -2372,25 +2435,25 @@
         <v>32</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:11">
@@ -2398,25 +2461,25 @@
         <v>32</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:11">
@@ -2424,25 +2487,25 @@
         <v>32</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:11">
@@ -2450,25 +2513,25 @@
         <v>32</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:11">
@@ -2476,13 +2539,13 @@
         <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>29</v>
@@ -2494,7 +2557,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:11">
@@ -2502,16 +2565,16 @@
         <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>40</v>
@@ -2520,7 +2583,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:11">
@@ -2528,13 +2591,13 @@
         <v>32</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>29</v>
@@ -2546,7 +2609,7 @@
         <v>29</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:11">
@@ -2554,16 +2617,16 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>40</v>
@@ -2572,7 +2635,7 @@
         <v>29</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:11">
@@ -2580,16 +2643,16 @@
         <v>32</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>45</v>
@@ -2598,7 +2661,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:11">
@@ -2606,13 +2669,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>29</v>
@@ -2624,7 +2687,7 @@
         <v>29</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:11">
@@ -2632,16 +2695,16 @@
         <v>32</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>40</v>
@@ -2650,7 +2713,7 @@
         <v>29</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:11">
@@ -2658,16 +2721,16 @@
         <v>32</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>45</v>
@@ -2676,7 +2739,7 @@
         <v>29</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:11">
@@ -2684,13 +2747,13 @@
         <v>32</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>29</v>
@@ -2702,7 +2765,7 @@
         <v>29</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:11">
@@ -2710,16 +2773,16 @@
         <v>32</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>40</v>
@@ -2728,7 +2791,7 @@
         <v>29</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:11">
@@ -2736,16 +2799,16 @@
         <v>32</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>45</v>
@@ -2754,7 +2817,7 @@
         <v>29</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:11">
@@ -2762,16 +2825,16 @@
         <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>50</v>
@@ -2780,7 +2843,7 @@
         <v>29</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:11">
@@ -2788,13 +2851,13 @@
         <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>29</v>
@@ -2806,7 +2869,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="17" spans="1:11">
@@ -2814,16 +2877,16 @@
         <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -2832,7 +2895,7 @@
         <v>29</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:11">
@@ -2840,13 +2903,13 @@
         <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>29</v>
@@ -2858,7 +2921,7 @@
         <v>29</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" ht="17" spans="1:11">
@@ -2866,16 +2929,16 @@
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>40</v>
@@ -2884,7 +2947,7 @@
         <v>29</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="17" spans="1:11">
@@ -2892,16 +2955,16 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>45</v>
@@ -2910,7 +2973,7 @@
         <v>29</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" ht="17" spans="1:11">
@@ -2918,16 +2981,16 @@
         <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>50</v>
@@ -2936,7 +2999,7 @@
         <v>29</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" ht="17" spans="1:11">
@@ -2944,25 +3007,25 @@
         <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" ht="17" spans="1:11">
@@ -2970,25 +3033,25 @@
         <v>32</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" ht="17" spans="1:11">
@@ -2996,25 +3059,25 @@
         <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:11">
@@ -3022,25 +3085,25 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3071,101 +3134,101 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" ht="135" spans="1:12">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" ht="152" spans="1:12">
       <c r="A2" s="8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:12">
       <c r="A3" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>140</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3205,7 +3268,7 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="17" spans="1:20">
       <c r="A1" s="7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
@@ -3214,75 +3277,75 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:20">
       <c r="A2" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>29</v>
@@ -3300,27 +3363,27 @@
         <v>29</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:20">
       <c r="A3" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>29</v>
@@ -3338,27 +3401,27 @@
         <v>29</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:20">
       <c r="A4" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
@@ -3376,7 +3439,7 @@
         <v>29</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3414,28 +3477,28 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -3444,472 +3507,472 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="T8" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3934,136 +3997,136 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="B15" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="B16" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
+++ b/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25900" windowHeight="13260" tabRatio="740" activeTab="1"/>
+    <workbookView windowHeight="14460" tabRatio="740"/>
   </bookViews>
   <sheets>
     <sheet name="Module" sheetId="19" r:id="rId1"/>
@@ -523,10 +523,10 @@
     <t>JeeSite 快速开发平台</t>
   </si>
   <si>
-    <t>JeeSite 快速开发平台，不仅仅是一个后台开发框架，它是一个企业级快速开发解决方案，后端基于经典组合 Spring Boot、Shiro、MyBatis，前端采用 Beetl、Bootstrap、AdminLTE 经典开发模式，或者分离版 Vue3、Vite、Ant Design Vue、TypeScript、Vben Admin 最先进技术栈。提供在线代码生成功能，支持 Spring Cloud 架构，分布式，微服务，微内核，信息化领域的专家。</t>
-  </si>
-  <si>
-    <t>&lt;!--HTML--&gt;&lt;p&gt;Copyright © 2024 演示站 - Powered By JeeSite V5&lt;/p&gt;</t>
+    <t>JeeSite 快速开发平台，低代码，轻量级，不仅仅是一个后台开发框架，它是一个企业级快速开发解决方案，后端基于经典组合 Spring Boot、Shiro、MyBatis，前端采用分离版 Vue3、Vite、Ant Design Vue、TypeScript、Vben Admin 最先进技术栈，或者 Beetl、Bootstrap、AdminLTE 经典开发模式。提供在线代码生成功能，支持 Spring Cloud 架构，分布式，微服务，微内核，信息化领域的专家。</t>
+  </si>
+  <si>
+    <t>&lt;!--HTML--&gt;&lt;p&gt;Copyright © 2026 演示站 - Powered By JeeSite V5&lt;/p&gt;</t>
   </si>
   <si>
     <t>index</t>
@@ -3170,7 +3170,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" ht="135" spans="1:12">
+    <row r="2" ht="152" spans="1:12">
       <c r="A2" s="8" t="s">
         <v>145</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>186</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>192</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>193</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>194</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>195</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>196</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>197</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>198</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>200</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>201</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>205</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>206</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>207</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>208</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>209</v>
       </c>

--- a/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
+++ b/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14460" tabRatio="740"/>
+    <workbookView windowHeight="15220" tabRatio="740" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Module" sheetId="19" r:id="rId1"/>
@@ -181,7 +181,7 @@
     <t>60</t>
   </si>
   <si>
-    <t>/cms/category/list</t>
+    <t>/cms/category/index</t>
   </si>
   <si>
     <t>cms:category</t>

--- a/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
+++ b/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="221">
   <si>
     <t>moduleCode</t>
   </si>
@@ -154,64 +154,79 @@
     <t>icon-social-dropbox</t>
   </si>
   <si>
+    <t>__id__index</t>
+  </si>
+  <si>
+    <t>内容发布</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>/cms/index</t>
+  </si>
+  <si>
+    <t>cms:view</t>
+  </si>
+  <si>
+    <t>icon-book-open</t>
+  </si>
+  <si>
     <t>__id__</t>
   </si>
   <si>
-    <t>内容发布</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>/cms/index</t>
+    <t>编辑文章</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>/cms/article/form</t>
+  </si>
+  <si>
+    <t>cms:article</t>
+  </si>
+  <si>
+    <t>栏目管理</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>/cms/category/index</t>
+  </si>
+  <si>
+    <t>cms:category</t>
+  </si>
+  <si>
+    <t>icon-plus</t>
+  </si>
+  <si>
+    <t>站点设置</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>/cms/site/list</t>
+  </si>
+  <si>
+    <t>cms:site</t>
+  </si>
+  <si>
+    <t>icon-badge</t>
+  </si>
+  <si>
+    <t>模版管理</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>/cms/template/list</t>
   </si>
   <si>
     <t>IFRAME</t>
-  </si>
-  <si>
-    <t>cms:view,cms:article</t>
-  </si>
-  <si>
-    <t>icon-book-open</t>
-  </si>
-  <si>
-    <t>栏目管理</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>/cms/category/index</t>
-  </si>
-  <si>
-    <t>cms:category</t>
-  </si>
-  <si>
-    <t>icon-plus</t>
-  </si>
-  <si>
-    <t>站点设置</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>/cms/site/list</t>
-  </si>
-  <si>
-    <t>cms:site</t>
-  </si>
-  <si>
-    <t>icon-badge</t>
-  </si>
-  <si>
-    <t>模版管理</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>/cms/template/list</t>
   </si>
   <si>
     <t>cms:template</t>
@@ -406,9 +421,6 @@
     <t>原创</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>轮播图</t>
   </si>
   <si>
@@ -740,7 +752,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,6 +778,13 @@
     <font>
       <sz val="11"/>
       <color theme="7" tint="0.399975585192419"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.25"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1238,137 +1257,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1409,7 +1428,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1812,8 +1834,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="9.10714285714286" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.2232142857143" style="4" customWidth="1"/>
@@ -1942,14 +1964,12 @@
       <c r="I3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="8"/>
+      <c r="M3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>29</v>
@@ -1963,19 +1983,19 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>30</v>
@@ -1983,15 +2003,11 @@
       <c r="I4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>36</v>
-      </c>
+      <c r="K4" s="8"/>
       <c r="M4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="N4" s="5"/>
       <c r="P4" s="5" t="s">
         <v>29</v>
       </c>
@@ -2004,16 +2020,16 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>29</v>
@@ -2022,16 +2038,14 @@
         <v>30</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="M5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>29</v>
@@ -2045,16 +2059,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>29</v>
@@ -2063,16 +2077,14 @@
         <v>30</v>
       </c>
       <c r="I6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="M6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>29</v>
@@ -2086,16 +2098,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>29</v>
@@ -2103,23 +2115,64 @@
       <c r="H7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="P7" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="1:16">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="N7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="N8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I7" r:id="rId3" display="https://vue.jeesite.com/cms/chat/index"/>
+    <hyperlink ref="I8" r:id="rId3" display="https://vue.jeesite.com/cms/chat/index"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2142,21 +2195,21 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>29</v>
@@ -2164,10 +2217,10 @@
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>29</v>
@@ -2175,10 +2228,10 @@
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>29</v>
@@ -2186,10 +2239,10 @@
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>29</v>
@@ -2197,10 +2250,10 @@
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>29</v>
@@ -2208,10 +2261,10 @@
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>29</v>
@@ -2219,10 +2272,10 @@
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>29</v>
@@ -2230,10 +2283,10 @@
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>29</v>
@@ -2267,51 +2320,51 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="17" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>25</v>
@@ -2323,24 +2376,24 @@
         <v>29</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:11">
       <c r="A3" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>34</v>
@@ -2349,255 +2402,255 @@
         <v>29</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:11">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:11">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:11">
       <c r="A6" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:11">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:11">
       <c r="A12" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:11">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>29</v>
@@ -2609,73 +2662,73 @@
         <v>29</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:11">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:11">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:11">
       <c r="A16" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>29</v>
@@ -2687,73 +2740,73 @@
         <v>29</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:11">
       <c r="A18" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:11">
       <c r="A19" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>29</v>
@@ -2765,99 +2818,99 @@
         <v>29</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:11">
       <c r="A20" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:11">
       <c r="A21" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:11">
       <c r="A22" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:11">
       <c r="A23" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>29</v>
@@ -2869,47 +2922,47 @@
         <v>29</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" ht="17" spans="1:11">
       <c r="A24" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:11">
       <c r="A25" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>29</v>
@@ -2921,189 +2974,189 @@
         <v>29</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" ht="17" spans="1:11">
       <c r="A26" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" ht="17" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" ht="17" spans="1:11">
       <c r="A28" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" ht="17" spans="1:11">
       <c r="A29" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" ht="17" spans="1:11">
       <c r="A30" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" ht="17" spans="1:11">
       <c r="A31" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:11">
       <c r="A32" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3134,101 +3187,101 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" ht="152" spans="1:12">
       <c r="A2" s="8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:12">
       <c r="A3" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="L3" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3268,7 +3321,7 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="17" spans="1:20">
       <c r="A1" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
@@ -3277,75 +3330,75 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:20">
       <c r="A2" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>29</v>
@@ -3363,27 +3416,27 @@
         <v>29</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:20">
       <c r="A3" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>29</v>
@@ -3401,27 +3454,27 @@
         <v>29</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:20">
       <c r="A4" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
@@ -3439,7 +3492,7 @@
         <v>29</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3477,28 +3530,28 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -3507,472 +3560,472 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3997,136 +4050,136 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
+++ b/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15220" tabRatio="740" activeTab="1"/>
+    <workbookView windowWidth="23540" windowHeight="9460" tabRatio="740" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Module" sheetId="19" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="220">
   <si>
     <t>moduleCode</t>
   </si>
@@ -223,10 +223,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>/cms/template/list</t>
-  </si>
-  <si>
-    <t>IFRAME</t>
+    <t>/cms/template/index</t>
   </si>
   <si>
     <t>cms:template</t>
@@ -1387,7 +1384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1430,9 +1427,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2007,7 +2001,6 @@
       <c r="M4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="5"/>
       <c r="P4" s="5" t="s">
         <v>29</v>
       </c>
@@ -2118,14 +2111,12 @@
       <c r="I7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="8"/>
+      <c r="M7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>29</v>
@@ -2139,16 +2130,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>29</v>
@@ -2156,24 +2147,21 @@
       <c r="H8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="K8" s="8"/>
       <c r="N8" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I8" r:id="rId3" display="https://vue.jeesite.com/cms/chat/index"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2195,21 +2183,21 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>29</v>
@@ -2217,10 +2205,10 @@
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>29</v>
@@ -2228,10 +2216,10 @@
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>29</v>
@@ -2239,10 +2227,10 @@
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>29</v>
@@ -2250,10 +2238,10 @@
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>29</v>
@@ -2261,10 +2249,10 @@
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>29</v>
@@ -2272,10 +2260,10 @@
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>29</v>
@@ -2283,10 +2271,10 @@
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>29</v>
@@ -2320,37 +2308,37 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="17" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:11">
@@ -2358,13 +2346,13 @@
         <v>38</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>25</v>
@@ -2376,7 +2364,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:11">
@@ -2384,16 +2372,16 @@
         <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>34</v>
@@ -2402,7 +2390,7 @@
         <v>29</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:11">
@@ -2410,16 +2398,16 @@
         <v>38</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>44</v>
@@ -2428,7 +2416,7 @@
         <v>29</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:11">
@@ -2436,16 +2424,16 @@
         <v>38</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>49</v>
@@ -2454,7 +2442,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:11">
@@ -2462,16 +2450,16 @@
         <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>54</v>
@@ -2480,7 +2468,7 @@
         <v>29</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:11">
@@ -2488,25 +2476,25 @@
         <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:11">
@@ -2514,25 +2502,25 @@
         <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="G8" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:11">
@@ -2540,25 +2528,25 @@
         <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="G9" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:11">
@@ -2566,25 +2554,25 @@
         <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="G10" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:11">
@@ -2592,13 +2580,13 @@
         <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>29</v>
@@ -2610,7 +2598,7 @@
         <v>29</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:11">
@@ -2618,13 +2606,13 @@
         <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>40</v>
@@ -2636,7 +2624,7 @@
         <v>29</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:11">
@@ -2644,13 +2632,13 @@
         <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>29</v>
@@ -2662,7 +2650,7 @@
         <v>29</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:11">
@@ -2670,13 +2658,13 @@
         <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>40</v>
@@ -2688,7 +2676,7 @@
         <v>29</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:11">
@@ -2696,16 +2684,16 @@
         <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>49</v>
@@ -2714,7 +2702,7 @@
         <v>29</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:11">
@@ -2722,13 +2710,13 @@
         <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>29</v>
@@ -2740,7 +2728,7 @@
         <v>29</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:11">
@@ -2748,13 +2736,13 @@
         <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>40</v>
@@ -2766,7 +2754,7 @@
         <v>29</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:11">
@@ -2774,16 +2762,16 @@
         <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>49</v>
@@ -2792,7 +2780,7 @@
         <v>29</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:11">
@@ -2800,13 +2788,13 @@
         <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>29</v>
@@ -2818,7 +2806,7 @@
         <v>29</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:11">
@@ -2826,13 +2814,13 @@
         <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>40</v>
@@ -2844,7 +2832,7 @@
         <v>29</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:11">
@@ -2852,16 +2840,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>49</v>
@@ -2870,7 +2858,7 @@
         <v>29</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:11">
@@ -2878,16 +2866,16 @@
         <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>54</v>
@@ -2896,7 +2884,7 @@
         <v>29</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:11">
@@ -2904,13 +2892,13 @@
         <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>29</v>
@@ -2922,7 +2910,7 @@
         <v>29</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" ht="17" spans="1:11">
@@ -2930,13 +2918,13 @@
         <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>40</v>
@@ -2948,7 +2936,7 @@
         <v>29</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:11">
@@ -2956,13 +2944,13 @@
         <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>29</v>
@@ -2974,7 +2962,7 @@
         <v>29</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="17" spans="1:11">
@@ -2982,13 +2970,13 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>40</v>
@@ -3000,7 +2988,7 @@
         <v>29</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="17" spans="1:11">
@@ -3008,16 +2996,16 @@
         <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>49</v>
@@ -3026,7 +3014,7 @@
         <v>29</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="17" spans="1:11">
@@ -3034,16 +3022,16 @@
         <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>54</v>
@@ -3052,7 +3040,7 @@
         <v>29</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" ht="17" spans="1:11">
@@ -3060,25 +3048,25 @@
         <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="F29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" ht="17" spans="1:11">
@@ -3086,25 +3074,25 @@
         <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="F30" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" ht="17" spans="1:11">
@@ -3112,25 +3100,25 @@
         <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F31" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:11">
@@ -3138,25 +3126,25 @@
         <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3187,101 +3175,101 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" ht="152" spans="1:12">
       <c r="A2" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="G2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>154</v>
-      </c>
       <c r="L2" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:12">
       <c r="A3" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3321,7 +3309,7 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="17" spans="1:20">
       <c r="A1" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
@@ -3330,75 +3318,75 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:20">
       <c r="A2" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>29</v>
@@ -3416,27 +3404,27 @@
         <v>29</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:20">
       <c r="A3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>29</v>
@@ -3454,27 +3442,27 @@
         <v>29</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:20">
       <c r="A4" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
@@ -3492,7 +3480,7 @@
         <v>29</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3530,28 +3518,28 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:20">
       <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -3560,112 +3548,112 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>40</v>
@@ -3674,56 +3662,56 @@
         <v>29</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>40</v>
@@ -3732,85 +3720,85 @@
         <v>40</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>40</v>
@@ -3819,85 +3807,85 @@
         <v>29</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>40</v>
@@ -3906,126 +3894,126 @@
         <v>29</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4050,136 +4038,136 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
+++ b/modules/cms/src/main/java/com/jeesite/modules/cms/db/InitCmsData.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23540" windowHeight="9460" tabRatio="740" activeTab="1"/>
+    <workbookView windowWidth="25820" windowHeight="10720" tabRatio="740" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Module" sheetId="19" r:id="rId1"/>
     <sheet name="Menu" sheetId="21" r:id="rId2"/>
     <sheet name="DictType" sheetId="22" r:id="rId3"/>
     <sheet name="DictData" sheetId="23" r:id="rId4"/>
-    <sheet name="Site" sheetId="25" r:id="rId5"/>
-    <sheet name="Category" sheetId="26" r:id="rId6"/>
-    <sheet name="Article" sheetId="27" r:id="rId7"/>
-    <sheet name="ArticleData" sheetId="28" r:id="rId8"/>
+    <sheet name="CmsSite" sheetId="25" r:id="rId5"/>
+    <sheet name="CmsCategory" sheetId="26" r:id="rId6"/>
+    <sheet name="CmsArticle" sheetId="27" r:id="rId7"/>
+    <sheet name="CmsArticleData" sheetId="28" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="221">
   <si>
     <t>moduleCode</t>
   </si>
@@ -548,6 +548,9 @@
   </si>
   <si>
     <t>子站点演示</t>
+  </si>
+  <si>
+    <t>子站描述信息</t>
   </si>
   <si>
     <t>&lt;!--HTML--&gt;&lt;p&gt;子站点样式&lt;/p&gt;</t>
@@ -3259,11 +3262,14 @@
       <c r="G3" s="8" t="s">
         <v>149</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="I3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>153</v>
@@ -3309,7 +3315,7 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="17" spans="1:20">
       <c r="A1" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
@@ -3318,22 +3324,22 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>143</v>
@@ -3342,28 +3348,28 @@
         <v>2</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>147</v>
@@ -3371,7 +3377,7 @@
     </row>
     <row r="2" ht="17" spans="1:20">
       <c r="A2" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>59</v>
@@ -3380,7 +3386,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>148</v>
@@ -3409,7 +3415,7 @@
     </row>
     <row r="3" ht="17" spans="1:20">
       <c r="A3" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>59</v>
@@ -3418,7 +3424,7 @@
         <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>148</v>
@@ -3447,7 +3453,7 @@
     </row>
     <row r="4" ht="17" spans="1:20">
       <c r="A4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>59</v>
@@ -3456,7 +3462,7 @@
         <v>49</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>148</v>
@@ -3518,25 +3524,25 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>143</v>
@@ -3548,31 +3554,31 @@
         <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>147</v>
@@ -3580,22 +3586,22 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>40</v>
@@ -3604,7 +3610,7 @@
         <v>59</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>59</v>
@@ -3612,16 +3618,16 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>59</v>
@@ -3633,7 +3639,7 @@
         <v>59</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>59</v>
@@ -3641,16 +3647,16 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>59</v>
@@ -3662,7 +3668,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>59</v>
@@ -3670,16 +3676,16 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>59</v>
@@ -3691,7 +3697,7 @@
         <v>131</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>59</v>
@@ -3699,16 +3705,16 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>59</v>
@@ -3720,7 +3726,7 @@
         <v>40</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>59</v>
@@ -3728,16 +3734,16 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>59</v>
@@ -3749,7 +3755,7 @@
         <v>131</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>59</v>
@@ -3757,16 +3763,16 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>59</v>
@@ -3778,7 +3784,7 @@
         <v>59</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>59</v>
@@ -3786,16 +3792,16 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>59</v>
@@ -3807,7 +3813,7 @@
         <v>29</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>59</v>
@@ -3815,16 +3821,16 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>59</v>
@@ -3836,7 +3842,7 @@
         <v>135</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>59</v>
@@ -3844,16 +3850,16 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>59</v>
@@ -3862,10 +3868,10 @@
         <v>40</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>59</v>
@@ -3873,16 +3879,16 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>59</v>
@@ -3894,7 +3900,7 @@
         <v>29</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>59</v>
@@ -3902,16 +3908,16 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>59</v>
@@ -3923,7 +3929,7 @@
         <v>59</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>59</v>
@@ -3931,16 +3937,16 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>59</v>
@@ -3952,7 +3958,7 @@
         <v>59</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>59</v>
@@ -3960,16 +3966,16 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>59</v>
@@ -3981,7 +3987,7 @@
         <v>59</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>59</v>
@@ -3989,16 +3995,16 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>59</v>
@@ -4010,7 +4016,7 @@
         <v>116</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>59</v>
@@ -4038,136 +4044,136 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
